--- a/batch_pre_sizing_casos.xlsx
+++ b/batch_pre_sizing_casos.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,212 +429,212 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Comprimento das longarinas (cm)</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Largura da pista disponível para longarinas (cm)</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>['Circular']</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Tipo de seção do tabuleiro</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Carga permanente atuante no tabuleiro (kN/m²) excluso peso próprio (kPa)</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Carga por roda (kN) (kN)</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Carga de multidão (kN/m²) (kPa)</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Distância entre eixos (m) do veículo tipo (m)</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Classe de carregamento</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Classe de madeira</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Classe de umidade</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>γg - Carga permanente</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>γq - Carga variável</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>γwc - Cisalhamento</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>γwf - Flexão</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>ψ2</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Coeficiente para fluência Tabela 20 NBR 7190</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Percentual de robustez</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Densidade da madeira (kg/m³) da longarina (kg/m³)</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Resistência característica à flexão (MPa) da longarina (MPa)</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Resistência característica ao cisalhamento (MPa) da longarina (MPa)</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Módulo de elasticidade à flexão (GPa) da longarina (GPa)</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Densidade da madeira (kg/m³) do tabuleiro (kg/m³)</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Resistência característica à flexão (MPa) do tabuleiro (MPa)</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>cfg_d_min</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>cfg_d_max</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>cfg_bw_min</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>cfg_bw_max</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>cfg_h_min</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>cfg_h_max</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>cfg_esp_long_min</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>cfg_esp_long_max</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>cfg_esp_tab_min</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>cfg_esp_tab_max</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>cfg_pop_size</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>cfg_n_gen</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>cfg_n_checagens</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>cfg_sobol</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>cfg_sobol_n_samples</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>cfg_ativo</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>cfg_subdiretorio</t>
         </is>
@@ -664,7 +676,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +688,7 @@
         <v>3</v>
       </c>
       <c r="M2" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="N2" t="n">
         <v>1.5</v>
@@ -691,7 +703,7 @@
         <v>0.3</v>
       </c>
       <c r="R2" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -700,7 +712,7 @@
         <v>500</v>
       </c>
       <c r="U2" t="n">
-        <v>25.97</v>
+        <v>20</v>
       </c>
       <c r="V2" t="n">
         <v>4</v>
@@ -712,7 +724,7 @@
         <v>500</v>
       </c>
       <c r="Y2" t="n">
-        <v>25.97</v>
+        <v>20</v>
       </c>
       <c r="Z2" t="n">
         <v>30</v>
@@ -800,7 +812,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -812,7 +824,7 @@
         <v>3</v>
       </c>
       <c r="M3" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="N3" t="n">
         <v>1.5</v>
@@ -827,7 +839,7 @@
         <v>0.3</v>
       </c>
       <c r="R3" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -836,7 +848,7 @@
         <v>625</v>
       </c>
       <c r="U3" t="n">
-        <v>38.96</v>
+        <v>30</v>
       </c>
       <c r="V3" t="n">
         <v>5</v>
@@ -848,7 +860,7 @@
         <v>625</v>
       </c>
       <c r="Y3" t="n">
-        <v>38.96</v>
+        <v>30</v>
       </c>
       <c r="Z3" t="n">
         <v>30</v>
@@ -936,7 +948,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -948,7 +960,7 @@
         <v>3</v>
       </c>
       <c r="M4" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="N4" t="n">
         <v>1.5</v>
@@ -963,7 +975,7 @@
         <v>0.3</v>
       </c>
       <c r="R4" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -972,7 +984,7 @@
         <v>750</v>
       </c>
       <c r="U4" t="n">
-        <v>51.95</v>
+        <v>40</v>
       </c>
       <c r="V4" t="n">
         <v>6</v>
@@ -984,7 +996,7 @@
         <v>750</v>
       </c>
       <c r="Y4" t="n">
-        <v>51.95</v>
+        <v>40</v>
       </c>
       <c r="Z4" t="n">
         <v>30</v>
@@ -1072,7 +1084,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1084,7 +1096,7 @@
         <v>3</v>
       </c>
       <c r="M5" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="N5" t="n">
         <v>1.5</v>
@@ -1099,7 +1111,7 @@
         <v>0.3</v>
       </c>
       <c r="R5" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1108,7 +1120,7 @@
         <v>850</v>
       </c>
       <c r="U5" t="n">
-        <v>64.94</v>
+        <v>50</v>
       </c>
       <c r="V5" t="n">
         <v>7</v>
@@ -1120,7 +1132,7 @@
         <v>850</v>
       </c>
       <c r="Y5" t="n">
-        <v>64.94</v>
+        <v>50</v>
       </c>
       <c r="Z5" t="n">
         <v>30</v>
@@ -1208,7 +1220,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1220,7 +1232,7 @@
         <v>3</v>
       </c>
       <c r="M6" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="N6" t="n">
         <v>1.5</v>
@@ -1235,7 +1247,7 @@
         <v>0.3</v>
       </c>
       <c r="R6" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1244,7 +1256,7 @@
         <v>1000</v>
       </c>
       <c r="U6" t="n">
-        <v>77.92</v>
+        <v>60</v>
       </c>
       <c r="V6" t="n">
         <v>8</v>
@@ -1256,7 +1268,7 @@
         <v>1000</v>
       </c>
       <c r="Y6" t="n">
-        <v>77.92</v>
+        <v>60</v>
       </c>
       <c r="Z6" t="n">
         <v>30</v>
@@ -1344,7 +1356,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1356,7 +1368,7 @@
         <v>3</v>
       </c>
       <c r="M7" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="N7" t="n">
         <v>1.5</v>
@@ -1371,7 +1383,7 @@
         <v>0.3</v>
       </c>
       <c r="R7" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1380,7 +1392,7 @@
         <v>500</v>
       </c>
       <c r="U7" t="n">
-        <v>25.97</v>
+        <v>20</v>
       </c>
       <c r="V7" t="n">
         <v>4</v>
@@ -1392,7 +1404,7 @@
         <v>500</v>
       </c>
       <c r="Y7" t="n">
-        <v>25.97</v>
+        <v>20</v>
       </c>
       <c r="Z7" t="n">
         <v>30</v>
@@ -1480,7 +1492,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1492,7 +1504,7 @@
         <v>3</v>
       </c>
       <c r="M8" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="N8" t="n">
         <v>1.5</v>
@@ -1507,7 +1519,7 @@
         <v>0.3</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1516,7 +1528,7 @@
         <v>625</v>
       </c>
       <c r="U8" t="n">
-        <v>38.96</v>
+        <v>30</v>
       </c>
       <c r="V8" t="n">
         <v>5</v>
@@ -1528,7 +1540,7 @@
         <v>625</v>
       </c>
       <c r="Y8" t="n">
-        <v>38.96</v>
+        <v>30</v>
       </c>
       <c r="Z8" t="n">
         <v>30</v>
@@ -1616,7 +1628,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1628,7 +1640,7 @@
         <v>3</v>
       </c>
       <c r="M9" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="N9" t="n">
         <v>1.5</v>
@@ -1643,7 +1655,7 @@
         <v>0.3</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1652,7 +1664,7 @@
         <v>750</v>
       </c>
       <c r="U9" t="n">
-        <v>51.95</v>
+        <v>40</v>
       </c>
       <c r="V9" t="n">
         <v>6</v>
@@ -1664,7 +1676,7 @@
         <v>750</v>
       </c>
       <c r="Y9" t="n">
-        <v>51.95</v>
+        <v>40</v>
       </c>
       <c r="Z9" t="n">
         <v>30</v>
@@ -1752,7 +1764,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1764,7 +1776,7 @@
         <v>3</v>
       </c>
       <c r="M10" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="N10" t="n">
         <v>1.5</v>
@@ -1779,7 +1791,7 @@
         <v>0.3</v>
       </c>
       <c r="R10" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1788,7 +1800,7 @@
         <v>850</v>
       </c>
       <c r="U10" t="n">
-        <v>64.94</v>
+        <v>50</v>
       </c>
       <c r="V10" t="n">
         <v>7</v>
@@ -1800,7 +1812,7 @@
         <v>850</v>
       </c>
       <c r="Y10" t="n">
-        <v>64.94</v>
+        <v>50</v>
       </c>
       <c r="Z10" t="n">
         <v>30</v>
@@ -1888,7 +1900,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1900,7 +1912,7 @@
         <v>3</v>
       </c>
       <c r="M11" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="N11" t="n">
         <v>1.5</v>
@@ -1915,7 +1927,7 @@
         <v>0.3</v>
       </c>
       <c r="R11" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1924,7 +1936,7 @@
         <v>1000</v>
       </c>
       <c r="U11" t="n">
-        <v>77.92</v>
+        <v>60</v>
       </c>
       <c r="V11" t="n">
         <v>8</v>
@@ -1936,7 +1948,7 @@
         <v>1000</v>
       </c>
       <c r="Y11" t="n">
-        <v>77.92</v>
+        <v>60</v>
       </c>
       <c r="Z11" t="n">
         <v>30</v>
@@ -2024,7 +2036,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -2036,7 +2048,7 @@
         <v>3</v>
       </c>
       <c r="M12" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="N12" t="n">
         <v>1.5</v>
@@ -2051,7 +2063,7 @@
         <v>0.3</v>
       </c>
       <c r="R12" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -2060,7 +2072,7 @@
         <v>500</v>
       </c>
       <c r="U12" t="n">
-        <v>25.97</v>
+        <v>20</v>
       </c>
       <c r="V12" t="n">
         <v>4</v>
@@ -2072,7 +2084,7 @@
         <v>500</v>
       </c>
       <c r="Y12" t="n">
-        <v>25.97</v>
+        <v>20</v>
       </c>
       <c r="Z12" t="n">
         <v>30</v>
@@ -2160,7 +2172,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -2172,7 +2184,7 @@
         <v>3</v>
       </c>
       <c r="M13" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="N13" t="n">
         <v>1.5</v>
@@ -2187,7 +2199,7 @@
         <v>0.3</v>
       </c>
       <c r="R13" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2196,7 +2208,7 @@
         <v>625</v>
       </c>
       <c r="U13" t="n">
-        <v>38.96</v>
+        <v>30</v>
       </c>
       <c r="V13" t="n">
         <v>5</v>
@@ -2208,7 +2220,7 @@
         <v>625</v>
       </c>
       <c r="Y13" t="n">
-        <v>38.96</v>
+        <v>30</v>
       </c>
       <c r="Z13" t="n">
         <v>30</v>
@@ -2296,7 +2308,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -2308,7 +2320,7 @@
         <v>3</v>
       </c>
       <c r="M14" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="N14" t="n">
         <v>1.5</v>
@@ -2323,7 +2335,7 @@
         <v>0.3</v>
       </c>
       <c r="R14" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2332,7 +2344,7 @@
         <v>750</v>
       </c>
       <c r="U14" t="n">
-        <v>51.95</v>
+        <v>40</v>
       </c>
       <c r="V14" t="n">
         <v>6</v>
@@ -2344,7 +2356,7 @@
         <v>750</v>
       </c>
       <c r="Y14" t="n">
-        <v>51.95</v>
+        <v>40</v>
       </c>
       <c r="Z14" t="n">
         <v>30</v>
@@ -2432,7 +2444,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -2444,7 +2456,7 @@
         <v>3</v>
       </c>
       <c r="M15" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="N15" t="n">
         <v>1.5</v>
@@ -2459,7 +2471,7 @@
         <v>0.3</v>
       </c>
       <c r="R15" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2468,7 +2480,7 @@
         <v>850</v>
       </c>
       <c r="U15" t="n">
-        <v>64.94</v>
+        <v>50</v>
       </c>
       <c r="V15" t="n">
         <v>7</v>
@@ -2480,7 +2492,7 @@
         <v>850</v>
       </c>
       <c r="Y15" t="n">
-        <v>64.94</v>
+        <v>50</v>
       </c>
       <c r="Z15" t="n">
         <v>30</v>
@@ -2568,7 +2580,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -2580,7 +2592,7 @@
         <v>3</v>
       </c>
       <c r="M16" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="N16" t="n">
         <v>1.5</v>
@@ -2595,7 +2607,7 @@
         <v>0.3</v>
       </c>
       <c r="R16" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2604,7 +2616,7 @@
         <v>1000</v>
       </c>
       <c r="U16" t="n">
-        <v>77.92</v>
+        <v>60</v>
       </c>
       <c r="V16" t="n">
         <v>8</v>
@@ -2616,7 +2628,7 @@
         <v>1000</v>
       </c>
       <c r="Y16" t="n">
-        <v>77.92</v>
+        <v>60</v>
       </c>
       <c r="Z16" t="n">
         <v>30</v>
@@ -2704,7 +2716,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -2716,7 +2728,7 @@
         <v>3</v>
       </c>
       <c r="M17" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="N17" t="n">
         <v>1.5</v>
@@ -2731,7 +2743,7 @@
         <v>0.3</v>
       </c>
       <c r="R17" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2740,7 +2752,7 @@
         <v>500</v>
       </c>
       <c r="U17" t="n">
-        <v>25.97</v>
+        <v>20</v>
       </c>
       <c r="V17" t="n">
         <v>4</v>
@@ -2752,7 +2764,7 @@
         <v>500</v>
       </c>
       <c r="Y17" t="n">
-        <v>25.97</v>
+        <v>20</v>
       </c>
       <c r="Z17" t="n">
         <v>30</v>
@@ -2840,7 +2852,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2852,7 +2864,7 @@
         <v>3</v>
       </c>
       <c r="M18" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="N18" t="n">
         <v>1.5</v>
@@ -2867,7 +2879,7 @@
         <v>0.3</v>
       </c>
       <c r="R18" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2876,7 +2888,7 @@
         <v>625</v>
       </c>
       <c r="U18" t="n">
-        <v>38.96</v>
+        <v>30</v>
       </c>
       <c r="V18" t="n">
         <v>5</v>
@@ -2888,7 +2900,7 @@
         <v>625</v>
       </c>
       <c r="Y18" t="n">
-        <v>38.96</v>
+        <v>30</v>
       </c>
       <c r="Z18" t="n">
         <v>30</v>
@@ -2976,7 +2988,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2988,7 +3000,7 @@
         <v>3</v>
       </c>
       <c r="M19" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="N19" t="n">
         <v>1.5</v>
@@ -3003,7 +3015,7 @@
         <v>0.3</v>
       </c>
       <c r="R19" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -3012,7 +3024,7 @@
         <v>750</v>
       </c>
       <c r="U19" t="n">
-        <v>51.95</v>
+        <v>40</v>
       </c>
       <c r="V19" t="n">
         <v>6</v>
@@ -3024,7 +3036,7 @@
         <v>750</v>
       </c>
       <c r="Y19" t="n">
-        <v>51.95</v>
+        <v>40</v>
       </c>
       <c r="Z19" t="n">
         <v>30</v>
@@ -3112,7 +3124,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -3124,7 +3136,7 @@
         <v>3</v>
       </c>
       <c r="M20" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="N20" t="n">
         <v>1.5</v>
@@ -3139,7 +3151,7 @@
         <v>0.3</v>
       </c>
       <c r="R20" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -3148,7 +3160,7 @@
         <v>850</v>
       </c>
       <c r="U20" t="n">
-        <v>64.94</v>
+        <v>50</v>
       </c>
       <c r="V20" t="n">
         <v>7</v>
@@ -3160,7 +3172,7 @@
         <v>850</v>
       </c>
       <c r="Y20" t="n">
-        <v>64.94</v>
+        <v>50</v>
       </c>
       <c r="Z20" t="n">
         <v>30</v>
@@ -3248,7 +3260,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>média duração</t>
+          <t>curta duração</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -3260,7 +3272,7 @@
         <v>3</v>
       </c>
       <c r="M21" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="N21" t="n">
         <v>1.5</v>
@@ -3275,7 +3287,7 @@
         <v>0.3</v>
       </c>
       <c r="R21" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3284,7 +3296,7 @@
         <v>1000</v>
       </c>
       <c r="U21" t="n">
-        <v>77.92</v>
+        <v>60</v>
       </c>
       <c r="V21" t="n">
         <v>8</v>
@@ -3296,7 +3308,7 @@
         <v>1000</v>
       </c>
       <c r="Y21" t="n">
-        <v>77.92</v>
+        <v>60</v>
       </c>
       <c r="Z21" t="n">
         <v>30</v>
